--- a/main/ig/FRAllergyIntoleranceLMCDAFHIR.xlsx
+++ b/main/ig/FRAllergyIntoleranceLMCDAFHIR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="81">
   <si>
     <t>Property</t>
   </si>
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T15:39:37+00:00</t>
+    <t>2026-08-05T12:15:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -79,7 +79,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Mapping des éléments du modèle métier FRLMAllergieOuHypersensibilite vers le profil CDA FRCDAAllergieOuHypersensibilite,puis vers le profil FHIR FRAllergyIntoleranceDocument.</t>
+    <t>Mapping des éléments du modèle métier FRLMAllergyIntolerance vers le profil CDA FRCDAAllergieOuHypersensibilite, puis vers le profil FHIR FRAllergyIntoleranceDocument.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -100,7 +100,7 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-allergie-ou-hypersensibilite</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-allergy-intolerance</t>
   </si>
   <si>
     <t/>
@@ -109,7 +109,7 @@
     <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-cda-allergie-ou-hypersensibilite</t>
   </si>
   <si>
-    <t>FRLMAllergieOuHypersensibilite</t>
+    <t>FRLMAllergyIntolerance</t>
   </si>
   <si>
     <t>equivalent</t>
@@ -118,61 +118,67 @@
     <t>FRCDAAllergieOuHypersensibilite</t>
   </si>
   <si>
-    <t>FRLMAllergieOuHypersensibilite.identifiant</t>
+    <t>FRLMAllergyIntolerance.header.identifier</t>
   </si>
   <si>
     <t>FRCDAAllergieOuHypersensibilite.id</t>
   </si>
   <si>
-    <t>FRLMAllergieOuHypersensibilite.description</t>
+    <t>FRLMAllergyIntolerance.note</t>
   </si>
   <si>
     <t>FRCDAAllergieOuHypersensibilite.text</t>
   </si>
   <si>
-    <t>FRLMAllergieOuHypersensibilite.type</t>
+    <t>FRLMAllergyIntolerance.type</t>
   </si>
   <si>
     <t>FRCDAAllergieOuHypersensibilite.code</t>
   </si>
   <si>
-    <t>FRLMAllergieOuHypersensibilite.statut</t>
-  </si>
-  <si>
-    <t>FRCDAAllergieOuHypersensibilite.statusCode</t>
-  </si>
-  <si>
-    <t>FRLMAllergieOuHypersensibilite.date</t>
+    <t>FRLMAllergyIntolerance.header.status</t>
+  </si>
+  <si>
+    <t>FRCDAAllergieOuHypersensibilite.entryRelationship:frStatutDuProbleme</t>
+  </si>
+  <si>
+    <t>FRLMAllergyIntolerance.period</t>
   </si>
   <si>
     <t>FRCDAAllergieOuHypersensibilite.effectiveTime</t>
   </si>
   <si>
-    <t>FRLMAllergieOuHypersensibilite.participant</t>
+    <t>FRLMAllergyIntolerance.period.onsetDate</t>
+  </si>
+  <si>
+    <t>FRCDAAllergieOuHypersensibilite.effectiveTime.low</t>
+  </si>
+  <si>
+    <t>FRLMAllergyIntolerance.period.endDate</t>
+  </si>
+  <si>
+    <t>FRCDAAllergieOuHypersensibilite.effectiveTime.high</t>
+  </si>
+  <si>
+    <t>FRLMAllergyIntolerance.agentOrAllergen</t>
   </si>
   <si>
     <t>FRCDAAllergieOuHypersensibilite.participant</t>
   </si>
   <si>
-    <t>FRLMAllergieOuHypersensibilite.probleme</t>
+    <t>FRLMAllergyIntolerance.reaction</t>
   </si>
   <si>
     <t>FRCDAAllergieOuHypersensibilite.entryRelationship:frProbleme</t>
   </si>
   <si>
-    <t>FRLMAllergieOuHypersensibilite.statutClique</t>
-  </si>
-  <si>
-    <t>FRCDAAllergieOuHypersensibilite.entryRelationship:frStatutCliniqueAllergie</t>
-  </si>
-  <si>
-    <t>FRLMAllergieOuHypersensibilite.certitude</t>
+    <t>FRLMAllergyIntolerance.certainty</t>
   </si>
   <si>
     <t>FRCDAAllergieOuHypersensibilite.entryRelationship:frCertitude</t>
   </si>
   <si>
-    <t>FRLMAllergieOuHypersensibilite.criticite</t>
+    <t>FRLMAllergyIntolerance.criticality</t>
   </si>
   <si>
     <t>FRCDAAllergieOuHypersensibilite.entryRelationship:frCriticite</t>
@@ -187,28 +193,70 @@
     <t>FRAllergyIntoleranceDocument.identifier</t>
   </si>
   <si>
-    <t>FRAllergyIntoleranceDocument.code.Text</t>
+    <t>FRAllergyIntoleranceDocument.note</t>
+  </si>
+  <si>
+    <t>FRAllergyIntoleranceDocument.type</t>
+  </si>
+  <si>
+    <t>FRAllergyIntoleranceDocument.clinicalStatus</t>
   </si>
   <si>
     <t>FRAllergyIntoleranceDocument.code</t>
   </si>
   <si>
+    <t>FRLMAllergyIntolerance.category</t>
+  </si>
+  <si>
+    <t>FRAllergyIntoleranceDocument.category</t>
+  </si>
+  <si>
     <t>FRAllergyIntoleranceDocument.onsetPeriod</t>
   </si>
   <si>
+    <t>FRAllergyIntoleranceDocument.onsetPeriod.start</t>
+  </si>
+  <si>
+    <t>FRAllergyIntoleranceDocument.onsetPeriod.end</t>
+  </si>
+  <si>
     <t>FRAllergyIntoleranceDocument.reaction</t>
   </si>
   <si>
+    <t>FRLMAllergyIntolerance.reaction.agentOrAllergen</t>
+  </si>
+  <si>
     <t>FRAllergyIntoleranceDocument.reaction.substance</t>
   </si>
   <si>
-    <t>FRAllergyIntoleranceDocument.clinicalStatus</t>
+    <t>FRLMAllergyIntolerance.reaction.manifestation</t>
+  </si>
+  <si>
+    <t>FRAllergyIntoleranceDocument.reaction.manifestation</t>
   </si>
   <si>
     <t>FRAllergyIntoleranceDocument.verificationStatus</t>
   </si>
   <si>
     <t>FRAllergyIntoleranceDocument.criticality</t>
+  </si>
+  <si>
+    <t>FRLMAllergyIntolerance.reaction.severity</t>
+  </si>
+  <si>
+    <t>FRAllergyIntoleranceDocument.reaction.severity</t>
+  </si>
+  <si>
+    <t>FRLMAllergyIntolerance.reaction.period</t>
+  </si>
+  <si>
+    <t>source-is-broader-than-target</t>
+  </si>
+  <si>
+    <t>FRAllergyIntoleranceDocument.reaction.onset</t>
+  </si>
+  <si>
+    <t>FRLMAllergyIntolerance.reaction.period.onsetDate</t>
   </si>
 </sst>
 </file>
@@ -460,7 +508,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -639,6 +687,19 @@
         <v>53</v>
       </c>
       <c r="E13" s="2"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="B14" s="2"/>
+      <c r="C14" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D14" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="E14" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -647,7 +708,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -669,7 +730,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>29</v>
@@ -678,7 +739,7 @@
         <v>29</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>29</v>
@@ -686,133 +747,237 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E12" s="2"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D13" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="B14" s="2"/>
+      <c r="C14" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D14" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="E14" s="2"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="B15" s="2"/>
+      <c r="C15" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E15" s="2"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="B16" s="2"/>
+      <c r="C16" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E16" s="2"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="B17" s="2"/>
+      <c r="C17" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E17" s="2"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="B18" s="2"/>
+      <c r="C18" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D18" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E18" s="2"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="B19" s="2"/>
+      <c r="C19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="D19" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E19" s="2"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="B20" s="2"/>
+      <c r="C20" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E20" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/main/ig/FRAllergyIntoleranceLMCDAFHIR.xlsx
+++ b/main/ig/FRAllergyIntoleranceLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:15:23+00:00</t>
+    <t>2026-08-11T08:03:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRAllergyIntoleranceLMCDAFHIR.xlsx
+++ b/main/ig/FRAllergyIntoleranceLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T08:03:55+00:00</t>
+    <t>2026-08-11T09:29:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRAllergyIntoleranceLMCDAFHIR.xlsx
+++ b/main/ig/FRAllergyIntoleranceLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T09:29:09+00:00</t>
+    <t>2026-08-13T09:45:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRAllergyIntoleranceLMCDAFHIR.xlsx
+++ b/main/ig/FRAllergyIntoleranceLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T09:45:33+00:00</t>
+    <t>2026-08-13T14:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRAllergyIntoleranceLMCDAFHIR.xlsx
+++ b/main/ig/FRAllergyIntoleranceLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T14:36:19+00:00</t>
+    <t>2026-08-14T12:00:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRAllergyIntoleranceLMCDAFHIR.xlsx
+++ b/main/ig/FRAllergyIntoleranceLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T12:00:06+00:00</t>
+    <t>2026-08-14T14:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRAllergyIntoleranceLMCDAFHIR.xlsx
+++ b/main/ig/FRAllergyIntoleranceLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T14:57:39+00:00</t>
+    <t>2026-08-20T08:45:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -100,13 +100,13 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-allergy-intolerance</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-allergy-intolerance|0.1.0</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-cda-allergie-ou-hypersensibilite</t>
+    <t>https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-allergie-ou-hypersensibilite|0.1.0</t>
   </si>
   <si>
     <t>FRLMAllergyIntolerance</t>
@@ -184,7 +184,7 @@
     <t>FRCDAAllergieOuHypersensibilite.entryRelationship:frCriticite</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-allergy-intolerance-document</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-allergy-intolerance-document|0.1.0</t>
   </si>
   <si>
     <t>FRAllergyIntoleranceDocument</t>

--- a/main/ig/FRAllergyIntoleranceLMCDAFHIR.xlsx
+++ b/main/ig/FRAllergyIntoleranceLMCDAFHIR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="84">
   <si>
     <t>Property</t>
   </si>
@@ -37,6 +37,9 @@
     <t>Name</t>
   </si>
   <si>
+    <t>FRAllergyIntoleranceLMCDAFHIR</t>
+  </si>
+  <si>
     <t>Title</t>
   </si>
   <si>
@@ -52,10 +55,13 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T08:45:34+00:00</t>
+    <t>2026-08-31T15:12:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -100,7 +106,7 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-allergy-intolerance|0.1.0</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMAllergyIntolerance|0.1.0</t>
   </si>
   <si>
     <t/>
@@ -115,136 +121,139 @@
     <t>equivalent</t>
   </si>
   <si>
+    <t>Observation</t>
+  </si>
+  <si>
     <t>FRCDAAllergieOuHypersensibilite</t>
   </si>
   <si>
     <t>FRLMAllergyIntolerance.header.identifier</t>
   </si>
   <si>
-    <t>FRCDAAllergieOuHypersensibilite.id</t>
+    <t>Observation.id</t>
   </si>
   <si>
     <t>FRLMAllergyIntolerance.note</t>
   </si>
   <si>
-    <t>FRCDAAllergieOuHypersensibilite.text</t>
+    <t>Observation.text</t>
   </si>
   <si>
     <t>FRLMAllergyIntolerance.type</t>
   </si>
   <si>
-    <t>FRCDAAllergieOuHypersensibilite.code</t>
+    <t>Observation.code</t>
   </si>
   <si>
     <t>FRLMAllergyIntolerance.header.status</t>
   </si>
   <si>
-    <t>FRCDAAllergieOuHypersensibilite.entryRelationship:frStatutDuProbleme</t>
+    <t>Observation.entryRelationship:frStatutDuProbleme</t>
   </si>
   <si>
     <t>FRLMAllergyIntolerance.period</t>
   </si>
   <si>
-    <t>FRCDAAllergieOuHypersensibilite.effectiveTime</t>
+    <t>Observation.effectiveTime</t>
   </si>
   <si>
     <t>FRLMAllergyIntolerance.period.onsetDate</t>
   </si>
   <si>
-    <t>FRCDAAllergieOuHypersensibilite.effectiveTime.low</t>
+    <t>source-is-narrower-than-target</t>
   </si>
   <si>
     <t>FRLMAllergyIntolerance.period.endDate</t>
   </si>
   <si>
-    <t>FRCDAAllergieOuHypersensibilite.effectiveTime.high</t>
-  </si>
-  <si>
     <t>FRLMAllergyIntolerance.agentOrAllergen</t>
   </si>
   <si>
-    <t>FRCDAAllergieOuHypersensibilite.participant</t>
+    <t>Observation.participant</t>
   </si>
   <si>
     <t>FRLMAllergyIntolerance.reaction</t>
   </si>
   <si>
-    <t>FRCDAAllergieOuHypersensibilite.entryRelationship:frProbleme</t>
+    <t>Observation.entryRelationship:frProbleme</t>
   </si>
   <si>
     <t>FRLMAllergyIntolerance.certainty</t>
   </si>
   <si>
-    <t>FRCDAAllergieOuHypersensibilite.entryRelationship:frCertitude</t>
+    <t>Observation.entryRelationship:frCertitude</t>
   </si>
   <si>
     <t>FRLMAllergyIntolerance.criticality</t>
   </si>
   <si>
-    <t>FRCDAAllergieOuHypersensibilite.entryRelationship:frCriticite</t>
+    <t>Observation.entryRelationship:frCriticite</t>
   </si>
   <si>
     <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-allergy-intolerance-document|0.1.0</t>
   </si>
   <si>
+    <t>AllergyIntolerance</t>
+  </si>
+  <si>
     <t>FRAllergyIntoleranceDocument</t>
   </si>
   <si>
-    <t>FRAllergyIntoleranceDocument.identifier</t>
-  </si>
-  <si>
-    <t>FRAllergyIntoleranceDocument.note</t>
-  </si>
-  <si>
-    <t>FRAllergyIntoleranceDocument.type</t>
-  </si>
-  <si>
-    <t>FRAllergyIntoleranceDocument.clinicalStatus</t>
-  </si>
-  <si>
-    <t>FRAllergyIntoleranceDocument.code</t>
+    <t>AllergyIntolerance.identifier</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.note</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.type</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.clinicalStatus</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.code</t>
   </si>
   <si>
     <t>FRLMAllergyIntolerance.category</t>
   </si>
   <si>
-    <t>FRAllergyIntoleranceDocument.category</t>
-  </si>
-  <si>
-    <t>FRAllergyIntoleranceDocument.onsetPeriod</t>
-  </si>
-  <si>
-    <t>FRAllergyIntoleranceDocument.onsetPeriod.start</t>
-  </si>
-  <si>
-    <t>FRAllergyIntoleranceDocument.onsetPeriod.end</t>
-  </si>
-  <si>
-    <t>FRAllergyIntoleranceDocument.reaction</t>
+    <t>AllergyIntolerance.category</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.onset[x]</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.onset[x]:onsetPeriod.start</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.onset[x]:onsetPeriod.end</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.reaction</t>
   </si>
   <si>
     <t>FRLMAllergyIntolerance.reaction.agentOrAllergen</t>
   </si>
   <si>
-    <t>FRAllergyIntoleranceDocument.reaction.substance</t>
+    <t>AllergyIntolerance.reaction.substance</t>
   </si>
   <si>
     <t>FRLMAllergyIntolerance.reaction.manifestation</t>
   </si>
   <si>
-    <t>FRAllergyIntoleranceDocument.reaction.manifestation</t>
-  </si>
-  <si>
-    <t>FRAllergyIntoleranceDocument.verificationStatus</t>
-  </si>
-  <si>
-    <t>FRAllergyIntoleranceDocument.criticality</t>
+    <t>AllergyIntolerance.reaction.manifestation</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.verificationStatus</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.criticality</t>
   </si>
   <si>
     <t>FRLMAllergyIntolerance.reaction.severity</t>
   </si>
   <si>
-    <t>FRAllergyIntoleranceDocument.reaction.severity</t>
+    <t>AllergyIntolerance.reaction.severity</t>
   </si>
   <si>
     <t>FRLMAllergyIntolerance.reaction.period</t>
@@ -253,7 +262,7 @@
     <t>source-is-broader-than-target</t>
   </si>
   <si>
-    <t>FRAllergyIntoleranceDocument.reaction.onset</t>
+    <t>AllergyIntolerance.reaction.onset</t>
   </si>
   <si>
     <t>FRLMAllergyIntolerance.reaction.period.onsetDate</t>
@@ -425,79 +434,83 @@
       <c r="A4" t="s" s="2">
         <v>6</v>
       </c>
-      <c r="B4" s="2"/>
+      <c r="B4" t="s" s="2">
+        <v>7</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>11</v>
-      </c>
-      <c r="B7" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
     </row>
@@ -513,191 +526,193 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s" s="1">
         <v>27</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>25</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="E3" s="2"/>
+        <v>35</v>
+      </c>
+      <c r="E3" t="s" s="2">
+        <v>36</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E14" s="2"/>
     </row>
@@ -713,269 +728,271 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s" s="1">
         <v>27</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>25</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>57</v>
-      </c>
-      <c r="E3" s="2"/>
+        <v>59</v>
+      </c>
+      <c r="E3" t="s" s="2">
+        <v>60</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E20" s="2"/>
     </row>

--- a/main/ig/FRAllergyIntoleranceLMCDAFHIR.xlsx
+++ b/main/ig/FRAllergyIntoleranceLMCDAFHIR.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T15:12:23+00:00</t>
+    <t>2026-09-04T14:19:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
